--- a/business_surveys/032_saas_industry_benchmark_survey--business_surveys.xlsx
+++ b/business_surveys/032_saas_industry_benchmark_survey--business_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1654,8 +1654,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="2" max="2"/>
+    <col width="29" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'less_than_10',_'value':_'less_than_10'}</t>
+          <t>less_than_10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Less than 10', 'value': 'less_than_10'}</t>
+          <t>Less than 10</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'10-49',_'value':_1049}</t>
+          <t>10-49</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '10-49', 'value': 1049}</t>
+          <t>10-49</t>
         </is>
       </c>
     </row>
@@ -1717,12 +1717,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'50-99',_'value':_5099}</t>
+          <t>50-99</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '50-99', 'value': 5099}</t>
+          <t>50-99</t>
         </is>
       </c>
     </row>
@@ -1734,12 +1734,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'100-499',_'value':_100499}</t>
+          <t>100-499</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '100-499', 'value': 100499}</t>
+          <t>100-499</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'500-999',_'value':_500999}</t>
+          <t>500-999</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': '500-999', 'value': 500999}</t>
+          <t>500-999</t>
         </is>
       </c>
     </row>
@@ -1768,12 +1768,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'1000+',_'value':_'1000_plus'}</t>
+          <t>1000+</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': '1000+', 'value': '1000_plus'}</t>
+          <t>1000+</t>
         </is>
       </c>
     </row>
@@ -1785,12 +1785,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'cost',_'value':_'cost'}</t>
+          <t>cost</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Cost', 'value': 'cost'}</t>
+          <t>Cost</t>
         </is>
       </c>
     </row>
@@ -1802,12 +1802,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'revenue',_'value':_'revenue'}</t>
+          <t>revenue</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Revenue', 'value': 'revenue'}</t>
+          <t>Revenue</t>
         </is>
       </c>
     </row>
@@ -1819,12 +1819,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'market_share',_'value':_'marketshare'}</t>
+          <t>market_share</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Market Share', 'value': 'marketshare'}</t>
+          <t>Market Share</t>
         </is>
       </c>
     </row>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'customer_engagement',_'value':_'engagement'}</t>
+          <t>customer_engagement</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Customer Engagement', 'value': 'engagement'}</t>
+          <t>Customer Engagement</t>
         </is>
       </c>
     </row>
@@ -1853,12 +1853,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_6,_'label':_'competitive_differentiation',_'value':_'differentiation'}</t>
+          <t>competitive_differentiation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 6, 'label': 'Competitive Differentiation', 'value': 'differentiation'}</t>
+          <t>Competitive Differentiation</t>
         </is>
       </c>
     </row>
